--- a/scores.xlsx
+++ b/scores.xlsx
@@ -8,15 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\rockpidinettrain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{502F0E6B-C17C-4DF6-9868-0E5FAE2C8C60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C12272D3-F295-40BB-8E7F-1DEC07B02BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="F-score" sheetId="1" r:id="rId1"/>
     <sheet name="ddn F-score" sheetId="4" r:id="rId2"/>
-    <sheet name="F-score-64" sheetId="3" r:id="rId3"/>
-    <sheet name="PQ" sheetId="2" r:id="rId4"/>
+    <sheet name="pidiet" sheetId="6" r:id="rId3"/>
+    <sheet name="rcf" sheetId="5" r:id="rId4"/>
+    <sheet name="ddn" sheetId="7" r:id="rId5"/>
+    <sheet name="F-score-64" sheetId="3" r:id="rId6"/>
+    <sheet name="PQ" sheetId="2" r:id="rId7"/>
+    <sheet name="Лист1" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="86">
   <si>
     <t>PiDiNet: boundary F-score</t>
   </si>
@@ -104,34 +108,199 @@
     <t>2, lam=0</t>
   </si>
   <si>
-    <t>0.407331272</t>
-  </si>
-  <si>
-    <t>0.517094720</t>
-  </si>
-  <si>
-    <t>0.620759754</t>
-  </si>
-  <si>
-    <t>0.339951643</t>
-  </si>
-  <si>
-    <t>0.500731744</t>
-  </si>
-  <si>
-    <t>0.344893136</t>
-  </si>
-  <si>
-    <t>0.499461871</t>
-  </si>
-  <si>
-    <t>0.545147906</t>
-  </si>
-  <si>
-    <t>0.362083740</t>
-  </si>
-  <si>
-    <t>0.401605489</t>
+    <t>ddn: boundary F-score</t>
+  </si>
+  <si>
+    <t>64_1</t>
+  </si>
+  <si>
+    <t>64_2</t>
+  </si>
+  <si>
+    <t>64_4</t>
+  </si>
+  <si>
+    <t>pq</t>
+  </si>
+  <si>
+    <t>0.02</t>
+  </si>
+  <si>
+    <t>0.09</t>
+  </si>
+  <si>
+    <t>0.03</t>
+  </si>
+  <si>
+    <t>0.01</t>
+  </si>
+  <si>
+    <t>0.04</t>
+  </si>
+  <si>
+    <t>0.018</t>
+  </si>
+  <si>
+    <t>0.08</t>
+  </si>
+  <si>
+    <t>0.12</t>
+  </si>
+  <si>
+    <t>0.06</t>
+  </si>
+  <si>
+    <t>rcf: boundary F-score</t>
+  </si>
+  <si>
+    <t>rcf: PQ</t>
+  </si>
+  <si>
+    <t>lam50, th64</t>
+  </si>
+  <si>
+    <t>Парамеры</t>
+  </si>
+  <si>
+    <t>lam0, th64</t>
+  </si>
+  <si>
+    <t>pidiet: PQ</t>
+  </si>
+  <si>
+    <t>pidinet: boundary F-score</t>
+  </si>
+  <si>
+    <t>25, 64</t>
+  </si>
+  <si>
+    <t>25, 32</t>
+  </si>
+  <si>
+    <t>50, 32</t>
+  </si>
+  <si>
+    <t>0, 64</t>
+  </si>
+  <si>
+    <t>Среднее</t>
+  </si>
+  <si>
+    <t>50, 0</t>
+  </si>
+  <si>
+    <t>50, 16</t>
+  </si>
+  <si>
+    <t>BSDS501</t>
+  </si>
+  <si>
+    <t>BSDS502</t>
+  </si>
+  <si>
+    <t>BSDS503</t>
+  </si>
+  <si>
+    <t>BSDS504</t>
+  </si>
+  <si>
+    <t>10, 32</t>
+  </si>
+  <si>
+    <t>ddn: PQ</t>
+  </si>
+  <si>
+    <t>rcf-&gt;pidi</t>
+  </si>
+  <si>
+    <t>25, 16</t>
+  </si>
+  <si>
+    <t>75, 16</t>
+  </si>
+  <si>
+    <t>100, 16</t>
+  </si>
+  <si>
+    <t>rcf-&gt;rcf</t>
+  </si>
+  <si>
+    <t>50, 64</t>
+  </si>
+  <si>
+    <t>125, 16</t>
+  </si>
+  <si>
+    <t>Целевой критерий PQ</t>
+  </si>
+  <si>
+    <t>Архетикура</t>
+  </si>
+  <si>
+    <t>PiDiNet</t>
+  </si>
+  <si>
+    <t>RCF</t>
+  </si>
+  <si>
+    <t>DDN</t>
+  </si>
+  <si>
+    <t>Модель</t>
+  </si>
+  <si>
+    <t>Selftrain</t>
+  </si>
+  <si>
+    <t>Оптимум λ, h</t>
+  </si>
+  <si>
+    <t>Метрика</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>PQ</t>
+  </si>
+  <si>
+    <t>Целевой критерий F1</t>
+  </si>
+  <si>
+    <t>&lt;0,01</t>
+  </si>
+  <si>
+    <t>rcf-&gt;ddn</t>
+  </si>
+  <si>
+    <t>0.3150618038659892</t>
+  </si>
+  <si>
+    <t>0.42057077906039075</t>
+  </si>
+  <si>
+    <t>0.5517273839342048</t>
+  </si>
+  <si>
+    <t>0.29814905013969695</t>
+  </si>
+  <si>
+    <t>0.45074526852257135</t>
+  </si>
+  <si>
+    <t>0.05378677506886571</t>
+  </si>
+  <si>
+    <t>0.08014287311752553</t>
+  </si>
+  <si>
+    <t>0.1696770404988994</t>
+  </si>
+  <si>
+    <t>0.03809120577179598</t>
+  </si>
+  <si>
+    <t>0.08825843163652212</t>
   </si>
 </sst>
 </file>
@@ -143,7 +312,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -205,6 +374,18 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF202B3C"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -251,7 +432,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -403,12 +584,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF334B6B"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
@@ -560,6 +750,20 @@
     <xf numFmtId="165" fontId="4" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -583,6 +787,33 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -912,13 +1143,13 @@
         <v>0.434096133</v>
       </c>
       <c r="E7" s="63"/>
-      <c r="F7" s="63" t="s">
-        <v>21</v>
+      <c r="F7" s="62">
+        <v>0.40733127200000002</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="19"/>
-      <c r="I7" t="s">
-        <v>26</v>
+      <c r="I7" s="45">
+        <v>0.34489313599999999</v>
       </c>
       <c r="K7" s="18"/>
       <c r="L7" s="19"/>
@@ -938,13 +1169,13 @@
         <v>0.51815958399999995</v>
       </c>
       <c r="E8" s="63"/>
-      <c r="F8" s="63" t="s">
-        <v>22</v>
+      <c r="F8" s="62">
+        <v>0.51709472000000001</v>
       </c>
       <c r="G8" s="64"/>
       <c r="H8" s="19"/>
-      <c r="I8" t="s">
-        <v>27</v>
+      <c r="I8" s="45">
+        <v>0.499461871</v>
       </c>
       <c r="K8" s="18"/>
       <c r="L8" s="19"/>
@@ -964,13 +1195,13 @@
         <v>0.642898423</v>
       </c>
       <c r="E9" s="63"/>
-      <c r="F9" s="63" t="s">
-        <v>23</v>
+      <c r="F9" s="62">
+        <v>0.62075975400000005</v>
       </c>
       <c r="G9" s="64"/>
       <c r="H9" s="19"/>
-      <c r="I9" t="s">
-        <v>28</v>
+      <c r="I9" s="45">
+        <v>0.54514790599999996</v>
       </c>
       <c r="K9" s="18"/>
       <c r="L9" s="19"/>
@@ -990,13 +1221,13 @@
         <v>0.31880282199999999</v>
       </c>
       <c r="E10" s="63"/>
-      <c r="F10" s="63" t="s">
-        <v>24</v>
+      <c r="F10" s="62">
+        <v>0.33995164300000003</v>
       </c>
       <c r="G10" s="64"/>
       <c r="H10" s="19"/>
-      <c r="I10" t="s">
-        <v>29</v>
+      <c r="I10" s="45">
+        <v>0.36208373999999999</v>
       </c>
       <c r="K10" s="18"/>
       <c r="L10" s="19"/>
@@ -1016,13 +1247,13 @@
         <v>0.54570070500000001</v>
       </c>
       <c r="E11" s="63"/>
-      <c r="F11" s="63" t="s">
-        <v>25</v>
+      <c r="F11" s="62">
+        <v>0.50073174399999998</v>
       </c>
       <c r="G11" s="64"/>
       <c r="H11" s="19"/>
-      <c r="I11" t="s">
-        <v>30</v>
+      <c r="I11" s="45">
+        <v>0.40160548899999998</v>
       </c>
       <c r="K11" s="18"/>
       <c r="L11" s="19"/>
@@ -1045,9 +1276,9 @@
         <v>0.49193153340000001</v>
       </c>
       <c r="E12" s="66"/>
-      <c r="F12" s="65" t="e">
+      <c r="F12" s="65">
         <f>AVERAGE(F7:F11)</f>
-        <v>#DIV/0!</v>
+        <v>0.47717382659999996</v>
       </c>
       <c r="G12" s="66" t="e">
         <f>AVERAGE(G7:G11)</f>
@@ -1055,6 +1286,10 @@
       </c>
       <c r="H12" s="21">
         <v>0.49968299799999999</v>
+      </c>
+      <c r="I12" s="65">
+        <f>AVERAGE(I7:I11)</f>
+        <v>0.4306384284</v>
       </c>
       <c r="K12" s="20"/>
       <c r="L12" s="21"/>
@@ -1073,13 +1308,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B40172B9-2564-4685-BE52-FD0A30AE3D13}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <sheetData>
-    <row r="1" spans="1:9" ht="21">
+    <row r="1" spans="1:11" ht="21">
       <c r="A1" s="5"/>
       <c r="B1" s="10" t="s">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C1" s="36"/>
       <c r="D1" s="36"/>
@@ -1089,7 +1324,7 @@
       <c r="H1" s="11"/>
       <c r="I1" s="12"/>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:11">
       <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
@@ -1100,7 +1335,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="32"/>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:11">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
@@ -1110,11 +1345,20 @@
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="F3" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="31" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
@@ -1124,11 +1368,26 @@
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
       <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="19"/>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="F4" s="63">
+        <v>0.3</v>
+      </c>
+      <c r="G4" s="64">
+        <v>0.21</v>
+      </c>
+      <c r="H4" s="19">
+        <v>0.11</v>
+      </c>
+      <c r="I4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
@@ -1136,11 +1395,26 @@
       <c r="C5" s="62"/>
       <c r="D5" s="62"/>
       <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="19"/>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="F5" s="63">
+        <v>0.35</v>
+      </c>
+      <c r="G5" s="64">
+        <v>0.24</v>
+      </c>
+      <c r="H5" s="19">
+        <v>0.16</v>
+      </c>
+      <c r="I5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
@@ -1148,11 +1422,26 @@
       <c r="C6" s="62"/>
       <c r="D6" s="62"/>
       <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="19"/>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="F6" s="63">
+        <v>0.5</v>
+      </c>
+      <c r="G6" s="64">
+        <v>0.34</v>
+      </c>
+      <c r="H6" s="19">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="I6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
@@ -1160,11 +1449,26 @@
       <c r="C7" s="62"/>
       <c r="D7" s="62"/>
       <c r="E7" s="63"/>
-      <c r="F7" s="63"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="19"/>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="F7" s="63">
+        <v>0.24</v>
+      </c>
+      <c r="G7" s="64">
+        <v>0.23</v>
+      </c>
+      <c r="H7" s="19">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="I7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" s="5" t="s">
         <v>7</v>
       </c>
@@ -1172,11 +1476,26 @@
       <c r="C8" s="62"/>
       <c r="D8" s="62"/>
       <c r="E8" s="63"/>
-      <c r="F8" s="63"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="19"/>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="F8" s="63">
+        <v>0.33</v>
+      </c>
+      <c r="G8" s="64">
+        <v>0.23</v>
+      </c>
+      <c r="H8" s="19">
+        <v>0.05</v>
+      </c>
+      <c r="I8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J8" t="s">
+        <v>28</v>
+      </c>
+      <c r="K8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" s="8" t="s">
         <v>8</v>
       </c>
@@ -1197,6 +1516,1391 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D11E2449-D761-4BC6-BC14-A812A0938C9C}">
+  <dimension ref="A1:P25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="2" width="11.5" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="21">
+      <c r="A1" s="5"/>
+      <c r="B1" s="67" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="H3" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="68">
+        <v>0.32</v>
+      </c>
+      <c r="C5" s="45">
+        <v>0.40600000000000003</v>
+      </c>
+      <c r="D5" s="45">
+        <v>0.36</v>
+      </c>
+      <c r="E5" s="45">
+        <v>0.34325988200000002</v>
+      </c>
+      <c r="F5" s="45">
+        <v>0.34337245399999999</v>
+      </c>
+      <c r="G5" s="45">
+        <v>0.34338326400000002</v>
+      </c>
+      <c r="H5" s="45">
+        <v>0.417390479813883</v>
+      </c>
+      <c r="I5" s="45"/>
+      <c r="J5">
+        <v>0.38648347721991499</v>
+      </c>
+      <c r="K5" s="45">
+        <v>0.29307578338696499</v>
+      </c>
+      <c r="L5" s="45"/>
+      <c r="M5" s="45"/>
+      <c r="N5" s="45"/>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="68">
+        <v>0.48</v>
+      </c>
+      <c r="C6" s="45">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="D6" s="45">
+        <v>0.50800000000000001</v>
+      </c>
+      <c r="E6" s="45">
+        <v>0.497969043</v>
+      </c>
+      <c r="F6" s="45">
+        <v>0.49018506000000001</v>
+      </c>
+      <c r="G6" s="45">
+        <v>0.498509918</v>
+      </c>
+      <c r="H6" s="45">
+        <v>0.523180952863739</v>
+      </c>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45">
+        <v>0.50989138213775098</v>
+      </c>
+      <c r="K6" s="45">
+        <v>0.47229643592972598</v>
+      </c>
+      <c r="L6" s="45"/>
+      <c r="M6" s="45"/>
+      <c r="N6" s="45"/>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="68">
+        <v>5.5829999999999998E-2</v>
+      </c>
+      <c r="C7" s="45">
+        <v>0.61070000000000002</v>
+      </c>
+      <c r="D7" s="45">
+        <v>0.58205410899999999</v>
+      </c>
+      <c r="E7" s="45">
+        <v>0.57320343600000001</v>
+      </c>
+      <c r="F7" s="45">
+        <v>0.57239377199999997</v>
+      </c>
+      <c r="G7" s="45">
+        <v>0.57327883300000004</v>
+      </c>
+      <c r="H7" s="45">
+        <v>0.63034344760838201</v>
+      </c>
+      <c r="I7" s="45"/>
+      <c r="J7" s="45">
+        <v>0.60845584922915397</v>
+      </c>
+      <c r="K7" s="45">
+        <v>0.525394435557899</v>
+      </c>
+      <c r="L7" s="45"/>
+      <c r="M7" s="45"/>
+      <c r="N7" s="45"/>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="68">
+        <v>0.34300000000000003</v>
+      </c>
+      <c r="C8" s="45">
+        <v>0.32359943899999999</v>
+      </c>
+      <c r="D8" s="45">
+        <v>0.33513280600000001</v>
+      </c>
+      <c r="E8" s="45">
+        <v>0.33479921699999998</v>
+      </c>
+      <c r="F8" s="45">
+        <v>0.33238287599999999</v>
+      </c>
+      <c r="G8" s="45">
+        <v>0.33466202900000003</v>
+      </c>
+      <c r="H8" s="45">
+        <v>0.30508713536291199</v>
+      </c>
+      <c r="I8" s="45"/>
+      <c r="J8" s="45">
+        <v>0.31620628451561</v>
+      </c>
+      <c r="K8" s="45">
+        <v>0.34186041212121099</v>
+      </c>
+      <c r="L8" s="45"/>
+      <c r="M8" s="45"/>
+      <c r="N8" s="45"/>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="68">
+        <v>0.42920000000000003</v>
+      </c>
+      <c r="C9" s="45">
+        <v>0.51610050200000002</v>
+      </c>
+      <c r="D9" s="45">
+        <v>0.465594864</v>
+      </c>
+      <c r="E9" s="45">
+        <v>0.45220607200000001</v>
+      </c>
+      <c r="F9" s="45">
+        <v>0.451406847</v>
+      </c>
+      <c r="G9" s="45">
+        <v>0.45224057400000001</v>
+      </c>
+      <c r="H9" s="45">
+        <v>0.53072347695633704</v>
+      </c>
+      <c r="I9" s="45"/>
+      <c r="J9" s="45">
+        <v>0.499110115849625</v>
+      </c>
+      <c r="K9" s="45">
+        <v>0.37990923911305602</v>
+      </c>
+      <c r="L9" s="45"/>
+      <c r="M9" s="45"/>
+      <c r="N9" s="45"/>
+    </row>
+    <row r="10" spans="1:14" ht="21.6" customHeight="1">
+      <c r="A10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="21">
+        <f t="shared" ref="B10:K10" si="0">AVERAGE(B5:B9)</f>
+        <v>0.32560600000000001</v>
+      </c>
+      <c r="C10" s="21">
+        <f t="shared" si="0"/>
+        <v>0.47587998819999999</v>
+      </c>
+      <c r="D10" s="21">
+        <f t="shared" si="0"/>
+        <v>0.45015635580000002</v>
+      </c>
+      <c r="E10" s="21">
+        <f t="shared" si="0"/>
+        <v>0.44028752999999998</v>
+      </c>
+      <c r="F10" s="21">
+        <f t="shared" si="0"/>
+        <v>0.43794820179999999</v>
+      </c>
+      <c r="G10" s="21">
+        <f t="shared" si="0"/>
+        <v>0.44041492360000001</v>
+      </c>
+      <c r="H10" s="21">
+        <f t="shared" si="0"/>
+        <v>0.48134509852105067</v>
+      </c>
+      <c r="I10" s="45"/>
+      <c r="J10" s="21">
+        <f>AVERAGE(J5:J9)</f>
+        <v>0.46402942179041096</v>
+      </c>
+      <c r="K10" s="21">
+        <f>AVERAGE(K5:K9)</f>
+        <v>0.40250726122177138</v>
+      </c>
+      <c r="L10" s="45"/>
+      <c r="M10" s="45"/>
+      <c r="N10" s="45"/>
+    </row>
+    <row r="16" spans="1:14" ht="21">
+      <c r="A16" s="5"/>
+      <c r="B16" s="67" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" s="9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="E18" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="F18" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="G18" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="H18" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" t="s">
+        <v>42</v>
+      </c>
+      <c r="E19" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" t="s">
+        <v>47</v>
+      </c>
+      <c r="G19" t="s">
+        <v>48</v>
+      </c>
+      <c r="H19" t="s">
+        <v>48</v>
+      </c>
+      <c r="I19" t="s">
+        <v>56</v>
+      </c>
+      <c r="J19" t="s">
+        <v>57</v>
+      </c>
+      <c r="K19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" s="19">
+        <v>3.7218465999999999E-2</v>
+      </c>
+      <c r="C20" s="70">
+        <v>1.3987197999999999E-2</v>
+      </c>
+      <c r="D20" s="70">
+        <v>3.3765554000000003E-2</v>
+      </c>
+      <c r="E20" s="70">
+        <v>4.2820744000000001E-2</v>
+      </c>
+      <c r="F20" s="45">
+        <v>4.2728588999999997E-2</v>
+      </c>
+      <c r="G20" s="45">
+        <v>4.2784941E-2</v>
+      </c>
+      <c r="H20" s="45">
+        <v>4.7094369629041302E-2</v>
+      </c>
+      <c r="I20" s="45">
+        <v>3.6997222320771198E-2</v>
+      </c>
+      <c r="J20" s="45">
+        <v>5.0304594449151502E-2</v>
+      </c>
+      <c r="K20" s="45">
+        <v>5.0726101321183999E-2</v>
+      </c>
+      <c r="L20" s="45"/>
+      <c r="M20" s="45"/>
+      <c r="N20" s="45"/>
+      <c r="O20" s="45"/>
+      <c r="P20" s="45"/>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="19">
+        <v>6.9221220999999999E-2</v>
+      </c>
+      <c r="C21" s="70">
+        <v>2.1191194999999999E-2</v>
+      </c>
+      <c r="D21" s="70">
+        <v>5.4892050999999997E-2</v>
+      </c>
+      <c r="E21" s="70">
+        <v>7.3807260999999999E-2</v>
+      </c>
+      <c r="F21" s="45">
+        <v>7.3286905999999999E-2</v>
+      </c>
+      <c r="G21" s="45">
+        <v>7.3742275999999995E-2</v>
+      </c>
+      <c r="H21" s="45">
+        <v>5.9285183089383402E-2</v>
+      </c>
+      <c r="I21" s="45">
+        <v>4.7043839530746097E-2</v>
+      </c>
+      <c r="J21" s="45">
+        <v>6.5665723480432495E-2</v>
+      </c>
+      <c r="K21" s="45">
+        <v>8.5322281035577804E-2</v>
+      </c>
+      <c r="L21" s="45"/>
+      <c r="M21" s="45"/>
+      <c r="N21" s="45"/>
+      <c r="O21" s="45"/>
+      <c r="P21" s="45"/>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="19">
+        <v>0.14858254900000001</v>
+      </c>
+      <c r="C22" s="70">
+        <v>6.2549336999999997E-2</v>
+      </c>
+      <c r="D22" s="70">
+        <v>0.12998521399999999</v>
+      </c>
+      <c r="E22" s="70">
+        <v>0.15788672600000001</v>
+      </c>
+      <c r="F22" s="45">
+        <v>0.15797713399999999</v>
+      </c>
+      <c r="G22" s="45">
+        <v>0.15845236100000001</v>
+      </c>
+      <c r="H22" s="45">
+        <v>0.170051686116966</v>
+      </c>
+      <c r="I22" s="45">
+        <v>0.146539142876631</v>
+      </c>
+      <c r="J22" s="45">
+        <v>0.18082925178859699</v>
+      </c>
+      <c r="K22" s="45">
+        <v>0.16355241751754299</v>
+      </c>
+      <c r="L22" s="45"/>
+      <c r="M22" s="45"/>
+      <c r="N22" s="45"/>
+      <c r="O22" s="45"/>
+      <c r="P22" s="45"/>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="19">
+        <v>3.2944888999999998E-2</v>
+      </c>
+      <c r="C23" s="70">
+        <v>6.262129E-3</v>
+      </c>
+      <c r="D23" s="70">
+        <v>2.3993153E-2</v>
+      </c>
+      <c r="E23" s="70">
+        <v>3.4055057E-2</v>
+      </c>
+      <c r="F23" s="45">
+        <v>3.3550207999999998E-2</v>
+      </c>
+      <c r="G23" s="45">
+        <v>3.3633726000000003E-2</v>
+      </c>
+      <c r="H23" s="45">
+        <v>2.1699616120661399E-2</v>
+      </c>
+      <c r="I23" s="45">
+        <v>1.6164016176619399E-2</v>
+      </c>
+      <c r="J23" s="45">
+        <v>2.9569832513109399E-2</v>
+      </c>
+      <c r="K23" s="45">
+        <v>4.3675376240422802E-2</v>
+      </c>
+      <c r="L23" s="45"/>
+      <c r="M23" s="45"/>
+      <c r="N23" s="45"/>
+      <c r="O23" s="45"/>
+      <c r="P23" s="45"/>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="19">
+        <v>5.9304678999999999E-2</v>
+      </c>
+      <c r="C24" s="70">
+        <v>3.6393218999999997E-2</v>
+      </c>
+      <c r="D24" s="70">
+        <v>5.8564214000000003E-2</v>
+      </c>
+      <c r="E24" s="70">
+        <v>6.5616483000000003E-2</v>
+      </c>
+      <c r="F24" s="45">
+        <v>6.5591788999999998E-2</v>
+      </c>
+      <c r="G24" s="45">
+        <v>6.5594140999999995E-2</v>
+      </c>
+      <c r="H24" s="45">
+        <v>9.2525400943434005E-2</v>
+      </c>
+      <c r="I24" s="45">
+        <v>8.7316305258767601E-2</v>
+      </c>
+      <c r="J24" s="45">
+        <v>8.7374883331797396E-2</v>
+      </c>
+      <c r="K24" s="45">
+        <v>6.9400873986287803E-2</v>
+      </c>
+      <c r="L24" s="45"/>
+      <c r="M24" s="45"/>
+      <c r="N24" s="45"/>
+      <c r="O24" s="45"/>
+      <c r="P24" s="45"/>
+    </row>
+    <row r="25" spans="1:16" ht="15.6" customHeight="1">
+      <c r="A25" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="21">
+        <f t="shared" ref="B25:K25" si="1">AVERAGE(B20:B24)</f>
+        <v>6.9454360800000003E-2</v>
+      </c>
+      <c r="C25" s="21">
+        <f t="shared" si="1"/>
+        <v>2.80766156E-2</v>
+      </c>
+      <c r="D25" s="21">
+        <f t="shared" si="1"/>
+        <v>6.0240037199999999E-2</v>
+      </c>
+      <c r="E25" s="21">
+        <f t="shared" si="1"/>
+        <v>7.4837254200000008E-2</v>
+      </c>
+      <c r="F25" s="21">
+        <f t="shared" si="1"/>
+        <v>7.4626925199999999E-2</v>
+      </c>
+      <c r="G25" s="21">
+        <f t="shared" si="1"/>
+        <v>7.4841488999999997E-2</v>
+      </c>
+      <c r="H25" s="21">
+        <f t="shared" si="1"/>
+        <v>7.8131251179897207E-2</v>
+      </c>
+      <c r="I25" s="21">
+        <f t="shared" si="1"/>
+        <v>6.6812105232707059E-2</v>
+      </c>
+      <c r="J25" s="21">
+        <f t="shared" si="1"/>
+        <v>8.2748857112617563E-2</v>
+      </c>
+      <c r="K25" s="21">
+        <f t="shared" si="1"/>
+        <v>8.2535410020203065E-2</v>
+      </c>
+      <c r="L25" s="45"/>
+      <c r="M25" s="45"/>
+      <c r="N25" s="45"/>
+      <c r="O25" s="45"/>
+      <c r="P25" s="45"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="11" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2EB4CFE-D3FF-4AD2-BAAD-8E29E8B78A31}">
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="15.09765625" customWidth="1"/>
+    <col min="2" max="2" width="10.796875" customWidth="1"/>
+    <col min="3" max="3" width="9.796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="21">
+      <c r="A1" s="5"/>
+      <c r="B1" s="67" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="68">
+        <v>0.41</v>
+      </c>
+      <c r="C5">
+        <v>0.44</v>
+      </c>
+      <c r="F5">
+        <v>0.40524875857669401</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="68">
+        <v>0.52</v>
+      </c>
+      <c r="C6">
+        <v>0.5</v>
+      </c>
+      <c r="F6">
+        <v>0.52775885648945098</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="68">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="C7">
+        <v>0.59</v>
+      </c>
+      <c r="F7">
+        <v>0.60916746088210905</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="68">
+        <v>0.3</v>
+      </c>
+      <c r="C8">
+        <v>0.24</v>
+      </c>
+      <c r="F8">
+        <v>0.33006072115505602</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="68">
+        <v>0.44</v>
+      </c>
+      <c r="C9">
+        <v>0.51</v>
+      </c>
+      <c r="F9">
+        <v>0.52574249764417802</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="69">
+        <f t="shared" ref="B10" si="0">AVERAGE(B5:B9)</f>
+        <v>0.45</v>
+      </c>
+      <c r="C10">
+        <v>0.46</v>
+      </c>
+      <c r="F10">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="21">
+      <c r="A13" s="5"/>
+      <c r="B13" s="67" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" t="s">
+        <v>58</v>
+      </c>
+      <c r="F16" t="s">
+        <v>48</v>
+      </c>
+      <c r="G16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="72">
+        <v>0.06</v>
+      </c>
+      <c r="C17" s="70">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="D17" s="70">
+        <v>5.9900000000000002E-2</v>
+      </c>
+      <c r="E17">
+        <v>5.43399861229166E-2</v>
+      </c>
+      <c r="F17">
+        <v>5.2027351534150001E-2</v>
+      </c>
+      <c r="G17">
+        <v>5.02936802061126E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="72">
+        <v>0.09</v>
+      </c>
+      <c r="C18" s="70">
+        <v>0.01</v>
+      </c>
+      <c r="D18" s="70">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="E18">
+        <v>8.4857591101279106E-2</v>
+      </c>
+      <c r="F18">
+        <v>7.33103211682547E-2</v>
+      </c>
+      <c r="G18">
+        <v>7.1206568897825395E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="72">
+        <v>0.15</v>
+      </c>
+      <c r="C19" s="70">
+        <v>0.02</v>
+      </c>
+      <c r="D19" s="70">
+        <v>0.151</v>
+      </c>
+      <c r="E19">
+        <v>0.17026732083613799</v>
+      </c>
+      <c r="F19">
+        <v>0.16068799808416601</v>
+      </c>
+      <c r="G19">
+        <v>0.15827126754513801</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="72">
+        <v>2.7184000999999999E-2</v>
+      </c>
+      <c r="C20" s="70">
+        <v>1E-3</v>
+      </c>
+      <c r="D20" s="70">
+        <v>2.8899999999999999E-2</v>
+      </c>
+      <c r="E20">
+        <v>4.2772681155411302E-2</v>
+      </c>
+      <c r="F20">
+        <v>3.3104008999754901E-2</v>
+      </c>
+      <c r="G20">
+        <v>3.3359978163438497E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="72">
+        <v>5.9439958000000001E-2</v>
+      </c>
+      <c r="C21" s="70">
+        <v>0.02</v>
+      </c>
+      <c r="D21" s="70">
+        <v>6.9199999999999998E-2</v>
+      </c>
+      <c r="E21">
+        <v>8.0892692839954705E-2</v>
+      </c>
+      <c r="F21">
+        <v>9.7758274365416203E-2</v>
+      </c>
+      <c r="G21">
+        <v>9.4191459040693704E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="21">
+        <f t="shared" ref="B22:E22" si="1">AVERAGE(B17:B21)</f>
+        <v>7.7324791800000001E-2</v>
+      </c>
+      <c r="C22" s="21">
+        <f t="shared" si="1"/>
+        <v>1.1200000000000002E-2</v>
+      </c>
+      <c r="D22" s="21">
+        <f t="shared" si="1"/>
+        <v>8.0399999999999999E-2</v>
+      </c>
+      <c r="E22" s="21">
+        <f>AVERAGE(E17:E21)</f>
+        <v>8.6626054411139949E-2</v>
+      </c>
+      <c r="F22" s="21">
+        <f>AVERAGE(F17:F21)</f>
+        <v>8.3377590830348375E-2</v>
+      </c>
+      <c r="G22" s="21">
+        <f>AVERAGE(G17:G21)</f>
+        <v>8.1464590770641637E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="11" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8FF53F6-1CBC-45DD-85B6-0D843C85863E}">
+  <dimension ref="A1:J25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="2" max="2" width="9.8984375" customWidth="1"/>
+    <col min="5" max="5" width="20.59765625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="21">
+      <c r="A1" s="5"/>
+      <c r="B1" s="67" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" s="35" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="68">
+        <v>0.28690741760871402</v>
+      </c>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45">
+        <v>0.29535421216839303</v>
+      </c>
+      <c r="J5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="68">
+        <v>0.40888285869561197</v>
+      </c>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45">
+        <v>0.40888285869561197</v>
+      </c>
+      <c r="J6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="68">
+        <v>0.460139707582712</v>
+      </c>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45">
+        <v>0.460139707582712</v>
+      </c>
+      <c r="J7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="68">
+        <v>0.279025405860095</v>
+      </c>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45">
+        <v>0.27868619727447602</v>
+      </c>
+      <c r="J8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="68">
+        <v>0.28424473442673598</v>
+      </c>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="45">
+        <v>0.30037923751692802</v>
+      </c>
+      <c r="J9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="21">
+        <f>AVERAGE(B5:B9)</f>
+        <v>0.34384002483477383</v>
+      </c>
+      <c r="C10" s="21" t="e">
+        <f t="shared" ref="C10:G10" si="0">AVERAGE(C5:C9)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D10" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E10" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F10" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G10" s="21">
+        <f t="shared" si="0"/>
+        <v>0.34868844264762422</v>
+      </c>
+      <c r="H10" s="21"/>
+    </row>
+    <row r="16" spans="1:10" ht="21">
+      <c r="A16" s="5"/>
+      <c r="B16" s="67" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="E18" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="J18" s="93" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" t="s">
+        <v>42</v>
+      </c>
+      <c r="E19" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" t="s">
+        <v>47</v>
+      </c>
+      <c r="G19" t="s">
+        <v>48</v>
+      </c>
+      <c r="H19" t="s">
+        <v>43</v>
+      </c>
+      <c r="I19" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" s="19">
+        <v>3.1734790542710202E-2</v>
+      </c>
+      <c r="C20" s="70"/>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70">
+        <v>3.2858445472339501E-2</v>
+      </c>
+      <c r="F20" s="45"/>
+      <c r="G20" s="45">
+        <v>3.2858445472339501E-2</v>
+      </c>
+      <c r="H20" s="45">
+        <v>3.6788339918729797E-2</v>
+      </c>
+      <c r="I20" s="45">
+        <v>3.0490420926095399E-2</v>
+      </c>
+      <c r="J20" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="19">
+        <v>7.4275663355559504E-2</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70">
+        <v>7.4275663355559504E-2</v>
+      </c>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45">
+        <v>7.4275663355559504E-2</v>
+      </c>
+      <c r="H21" s="45">
+        <v>8.5038681945984101E-2</v>
+      </c>
+      <c r="I21" s="45">
+        <v>8.0765217468929396E-2</v>
+      </c>
+      <c r="J21" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="19">
+        <v>0.104257965348204</v>
+      </c>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70">
+        <v>0.104257965348204</v>
+      </c>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45">
+        <v>0.104</v>
+      </c>
+      <c r="H22" s="45">
+        <v>0.10841106684937001</v>
+      </c>
+      <c r="I22" s="45">
+        <v>0.108799604934304</v>
+      </c>
+      <c r="J22" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="19">
+        <v>3.5526704822912099E-2</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70">
+        <v>3.60827264870393E-2</v>
+      </c>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45">
+        <v>3.60827264870393E-2</v>
+      </c>
+      <c r="H23" s="45">
+        <v>2.41389348925201E-2</v>
+      </c>
+      <c r="I23" s="45">
+        <v>1.40635761187795E-2</v>
+      </c>
+      <c r="J23" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="19">
+        <v>3.9867348991240503E-2</v>
+      </c>
+      <c r="C24" s="70"/>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70">
+        <v>4.02378423932458E-2</v>
+      </c>
+      <c r="F24" s="45"/>
+      <c r="G24" s="45">
+        <v>4.02378423932458E-2</v>
+      </c>
+      <c r="H24" s="45">
+        <v>6.1902086218172399E-2</v>
+      </c>
+      <c r="I24" s="45">
+        <v>7.7102667039015804E-2</v>
+      </c>
+      <c r="J24" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="21">
+        <f t="shared" ref="B25:I25" si="1">AVERAGE(B20:B24)</f>
+        <v>5.7132494612125259E-2</v>
+      </c>
+      <c r="C25" s="21" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D25" s="21" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E25" s="21">
+        <f>AVERAGE(E20:E24)</f>
+        <v>5.7542528611277621E-2</v>
+      </c>
+      <c r="F25" s="21" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G25" s="21">
+        <f t="shared" si="1"/>
+        <v>5.7490935541636826E-2</v>
+      </c>
+      <c r="H25" s="21">
+        <f t="shared" si="1"/>
+        <v>6.3255821964955286E-2</v>
+      </c>
+      <c r="I25" s="21">
+        <f t="shared" si="1"/>
+        <v>6.2244297297424825E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63E4173D-FFFB-4613-8853-3B75CBD16295}">
   <dimension ref="B5:K13"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
@@ -1458,23 +3162,23 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20ECF1A6-17CB-4F5E-8A81-EEB9AEA80637}">
   <dimension ref="B3:J11"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <sheetData>
     <row r="3" spans="2:10" ht="21">
       <c r="B3" s="5"/>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="69"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="75"/>
     </row>
     <row r="4" spans="2:10">
       <c r="B4" s="7" t="s">
@@ -1483,17 +3187,17 @@
       <c r="C4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="70" t="s">
+      <c r="D4" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="71"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="70" t="s">
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="I4" s="73"/>
-      <c r="J4" s="74"/>
+      <c r="I4" s="79"/>
+      <c r="J4" s="80"/>
     </row>
     <row r="5" spans="2:10">
       <c r="B5" s="6" t="s">
@@ -1652,4 +3356,601 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69DC4E0C-2F62-48EE-AC18-73073529A3D7}">
+  <dimension ref="C5:O39"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="3" max="3" width="15.296875" customWidth="1"/>
+    <col min="4" max="11" width="6.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="3:11">
+      <c r="C5" s="82" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="82"/>
+      <c r="K5" s="82"/>
+    </row>
+    <row r="6" spans="3:11">
+      <c r="C6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" s="83" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+    </row>
+    <row r="7" spans="3:11">
+      <c r="C7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="83" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83" t="s">
+        <v>68</v>
+      </c>
+      <c r="G7" s="83"/>
+    </row>
+    <row r="8" spans="3:11">
+      <c r="C8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>64</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="3:11">
+      <c r="C9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" t="s">
+        <v>72</v>
+      </c>
+      <c r="F9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="3:11">
+      <c r="C10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="68">
+        <v>0.29960101248690674</v>
+      </c>
+      <c r="E10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10" s="62">
+        <v>0.434096133</v>
+      </c>
+      <c r="G10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="3:11" ht="15.6" customHeight="1">
+      <c r="C11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="68">
+        <v>0.48782025625752629</v>
+      </c>
+      <c r="E11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F11" s="62">
+        <v>0.51815958399999995</v>
+      </c>
+      <c r="G11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="3:11">
+      <c r="C12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="68">
+        <v>0.52295169087459048</v>
+      </c>
+      <c r="E12" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" s="62">
+        <v>0.642898423</v>
+      </c>
+      <c r="G12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="3:11">
+      <c r="C13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="68">
+        <v>0.36544650811281948</v>
+      </c>
+      <c r="E13" t="s">
+        <v>74</v>
+      </c>
+      <c r="F13" s="62">
+        <v>0.31880282199999999</v>
+      </c>
+      <c r="G13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="3:11">
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="68">
+        <v>0.38352293822875039</v>
+      </c>
+      <c r="E14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" s="62">
+        <v>0.54570070500000001</v>
+      </c>
+      <c r="G14" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="3:11">
+      <c r="C15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="69">
+        <f t="shared" ref="D15" si="0">AVERAGE(D10:D14)</f>
+        <v>0.41186848119211861</v>
+      </c>
+      <c r="E15" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" s="65">
+        <f>AVERAGE(F10:F14)</f>
+        <v>0.49193153340000001</v>
+      </c>
+      <c r="G15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15">
+      <c r="C29" s="84" t="s">
+        <v>62</v>
+      </c>
+      <c r="D29" s="84"/>
+      <c r="E29" s="84"/>
+      <c r="F29" s="84"/>
+      <c r="G29" s="84"/>
+      <c r="H29" s="84"/>
+      <c r="I29" s="84"/>
+      <c r="J29" s="84"/>
+      <c r="K29" s="84"/>
+      <c r="L29" s="84"/>
+      <c r="M29" s="84"/>
+      <c r="N29" s="84"/>
+      <c r="O29" s="84"/>
+    </row>
+    <row r="30" spans="3:15">
+      <c r="C30" s="85" t="s">
+        <v>63</v>
+      </c>
+      <c r="D30" s="84" t="s">
+        <v>64</v>
+      </c>
+      <c r="E30" s="84"/>
+      <c r="F30" s="84"/>
+      <c r="G30" s="84"/>
+      <c r="H30" s="84" t="s">
+        <v>65</v>
+      </c>
+      <c r="I30" s="84"/>
+      <c r="J30" s="84"/>
+      <c r="K30" s="84"/>
+      <c r="L30" s="84" t="s">
+        <v>66</v>
+      </c>
+      <c r="M30" s="84"/>
+      <c r="N30" s="84"/>
+      <c r="O30" s="84"/>
+    </row>
+    <row r="31" spans="3:15">
+      <c r="C31" s="85" t="s">
+        <v>67</v>
+      </c>
+      <c r="D31" s="86" t="s">
+        <v>2</v>
+      </c>
+      <c r="E31" s="86"/>
+      <c r="F31" s="86" t="s">
+        <v>68</v>
+      </c>
+      <c r="G31" s="86"/>
+      <c r="H31" s="84" t="s">
+        <v>2</v>
+      </c>
+      <c r="I31" s="84"/>
+      <c r="J31" s="84" t="s">
+        <v>68</v>
+      </c>
+      <c r="K31" s="84"/>
+      <c r="L31" s="84" t="s">
+        <v>2</v>
+      </c>
+      <c r="M31" s="84"/>
+      <c r="N31" s="84" t="s">
+        <v>68</v>
+      </c>
+      <c r="O31" s="84"/>
+    </row>
+    <row r="32" spans="3:15">
+      <c r="C32" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="D32" s="86" t="s">
+        <v>48</v>
+      </c>
+      <c r="E32" s="86"/>
+      <c r="F32" s="86" t="s">
+        <v>57</v>
+      </c>
+      <c r="G32" s="86"/>
+      <c r="H32" s="85" t="s">
+        <v>48</v>
+      </c>
+      <c r="I32" s="85"/>
+      <c r="J32" s="85"/>
+      <c r="K32" s="85" t="s">
+        <v>58</v>
+      </c>
+      <c r="L32" s="85" t="s">
+        <v>53</v>
+      </c>
+      <c r="M32" s="85"/>
+      <c r="N32" s="85"/>
+      <c r="O32" s="85"/>
+    </row>
+    <row r="33" spans="3:15">
+      <c r="C33" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E33" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F33" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="G33" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="H33" s="85"/>
+      <c r="I33" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="J33" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="K33" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="L33" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="M33" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="N33" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="O33" s="85" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" spans="3:15">
+      <c r="C34" s="85" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="87">
+        <v>0.34325988200000002</v>
+      </c>
+      <c r="E34" s="87">
+        <v>4.2820744000000001E-2</v>
+      </c>
+      <c r="F34" s="87">
+        <v>0.38648347721991499</v>
+      </c>
+      <c r="G34" s="87">
+        <v>5.0304594449151502E-2</v>
+      </c>
+      <c r="H34" s="88">
+        <v>0.28690741760871402</v>
+      </c>
+      <c r="I34" s="87">
+        <v>5.9900000000000002E-2</v>
+      </c>
+      <c r="J34" s="87">
+        <v>0.40524875857669401</v>
+      </c>
+      <c r="K34" s="87">
+        <v>5.43399861229166E-2</v>
+      </c>
+      <c r="L34" s="88">
+        <v>0.28690741760871402</v>
+      </c>
+      <c r="M34" s="89">
+        <v>3.1734790542710202E-2</v>
+      </c>
+      <c r="N34" s="90">
+        <v>0</v>
+      </c>
+      <c r="O34" s="90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="3:15">
+      <c r="C35" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="D35" s="87">
+        <v>0.497969043</v>
+      </c>
+      <c r="E35" s="87">
+        <v>7.3807260999999999E-2</v>
+      </c>
+      <c r="F35" s="87">
+        <v>0.50989138213775098</v>
+      </c>
+      <c r="G35" s="87">
+        <v>6.5665723480432495E-2</v>
+      </c>
+      <c r="H35" s="88">
+        <v>0.40888285869561197</v>
+      </c>
+      <c r="I35" s="87">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="J35" s="87">
+        <v>0.52775885648945098</v>
+      </c>
+      <c r="K35" s="87">
+        <v>8.4857591101279106E-2</v>
+      </c>
+      <c r="L35" s="88">
+        <v>0.40888285869561197</v>
+      </c>
+      <c r="M35" s="89">
+        <v>7.4275663355559504E-2</v>
+      </c>
+      <c r="N35" s="90">
+        <v>0</v>
+      </c>
+      <c r="O35" s="90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="3:15">
+      <c r="C36" s="85" t="s">
+        <v>5</v>
+      </c>
+      <c r="D36" s="87">
+        <v>0.57320343600000001</v>
+      </c>
+      <c r="E36" s="87">
+        <v>0.15788672600000001</v>
+      </c>
+      <c r="F36" s="87">
+        <v>0.60845584922915397</v>
+      </c>
+      <c r="G36" s="87">
+        <v>0.18082925178859699</v>
+      </c>
+      <c r="H36" s="88">
+        <v>0.460139707582712</v>
+      </c>
+      <c r="I36" s="87">
+        <v>0.151</v>
+      </c>
+      <c r="J36" s="87">
+        <v>0.60916746088210905</v>
+      </c>
+      <c r="K36" s="87">
+        <v>0.17026732083613799</v>
+      </c>
+      <c r="L36" s="88">
+        <v>0.460139707582712</v>
+      </c>
+      <c r="M36" s="89">
+        <v>0.104257965348204</v>
+      </c>
+      <c r="N36" s="90">
+        <v>0</v>
+      </c>
+      <c r="O36" s="90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="3:15">
+      <c r="C37" s="85" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" s="87">
+        <v>0.33479921699999998</v>
+      </c>
+      <c r="E37" s="87">
+        <v>3.4055057E-2</v>
+      </c>
+      <c r="F37" s="87">
+        <v>0.31620628451561</v>
+      </c>
+      <c r="G37" s="87">
+        <v>2.9569832513109399E-2</v>
+      </c>
+      <c r="H37" s="88">
+        <v>0.279025405860095</v>
+      </c>
+      <c r="I37" s="87">
+        <v>2.8899999999999999E-2</v>
+      </c>
+      <c r="J37" s="87">
+        <v>0.33006072115505602</v>
+      </c>
+      <c r="K37" s="87">
+        <v>4.2772681155411302E-2</v>
+      </c>
+      <c r="L37" s="88">
+        <v>0.279025405860095</v>
+      </c>
+      <c r="M37" s="89">
+        <v>3.5526704822912099E-2</v>
+      </c>
+      <c r="N37" s="90">
+        <v>0</v>
+      </c>
+      <c r="O37" s="90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="3:15">
+      <c r="C38" s="85" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="87">
+        <v>0.45220607200000001</v>
+      </c>
+      <c r="E38" s="87">
+        <v>6.5616483000000003E-2</v>
+      </c>
+      <c r="F38" s="87">
+        <v>0.499110115849625</v>
+      </c>
+      <c r="G38" s="87">
+        <v>8.7374883331797396E-2</v>
+      </c>
+      <c r="H38" s="88">
+        <v>0.28424473442673598</v>
+      </c>
+      <c r="I38" s="87">
+        <v>6.9199999999999998E-2</v>
+      </c>
+      <c r="J38" s="87">
+        <v>0.52574249764417802</v>
+      </c>
+      <c r="K38" s="87">
+        <v>8.0892692839954705E-2</v>
+      </c>
+      <c r="L38" s="88">
+        <v>0.28424473442673598</v>
+      </c>
+      <c r="M38" s="89">
+        <v>3.9867348991240503E-2</v>
+      </c>
+      <c r="N38" s="90">
+        <v>0</v>
+      </c>
+      <c r="O38" s="90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="3:15">
+      <c r="C39" s="85" t="s">
+        <v>46</v>
+      </c>
+      <c r="D39" s="91">
+        <f t="shared" ref="D39" si="1">AVERAGE(D34:D38)</f>
+        <v>0.44028752999999998</v>
+      </c>
+      <c r="E39" s="91">
+        <f t="shared" ref="E39" si="2">AVERAGE(E34:E38)</f>
+        <v>7.4837254200000008E-2</v>
+      </c>
+      <c r="F39" s="92">
+        <f>AVERAGE(F34:F38)</f>
+        <v>0.46402942179041096</v>
+      </c>
+      <c r="G39" s="92">
+        <f t="shared" ref="G39:H39" si="3">AVERAGE(G34:G38)</f>
+        <v>8.2748857112617563E-2</v>
+      </c>
+      <c r="H39" s="91">
+        <f>AVERAGE(H34:H38)</f>
+        <v>0.34384002483477383</v>
+      </c>
+      <c r="I39" s="91">
+        <f>AVERAGE(I34:I38)</f>
+        <v>8.0399999999999999E-2</v>
+      </c>
+      <c r="J39" s="85">
+        <v>0.46</v>
+      </c>
+      <c r="K39" s="91">
+        <f>AVERAGE(K34:K38)</f>
+        <v>8.6626054411139949E-2</v>
+      </c>
+      <c r="L39" s="91">
+        <f>AVERAGE(L34:L38)</f>
+        <v>0.34384002483477383</v>
+      </c>
+      <c r="M39" s="91">
+        <f t="shared" ref="M39" si="4">AVERAGE(M34:M38)</f>
+        <v>5.7132494612125259E-2</v>
+      </c>
+      <c r="N39" s="90">
+        <v>0</v>
+      </c>
+      <c r="O39" s="90">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="C5:K5"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="L31:M31"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="H30:K30"/>
+    <mergeCell ref="L30:O30"/>
+    <mergeCell ref="C29:O29"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="J31:K31"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>